--- a/BD_SSJ.xlsx
+++ b/BD_SSJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorodrigu\Documents\Research\20251210-FPVRPTW\FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3127784-F8BC-4BC1-B590-3F50368D2CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294E6364-52F5-4C0E-8770-F499FB5BB732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7E20A6E5-5375-4A6A-9583-7CF4AF37259B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7E20A6E5-5375-4A6A-9583-7CF4AF37259B}"/>
   </bookViews>
   <sheets>
     <sheet name="SOURCES" sheetId="1" r:id="rId1"/>
@@ -7705,18 +7705,11 @@
     <numFmt numFmtId="165" formatCode="d\ m"/>
     <numFmt numFmtId="166" formatCode="d\ m\ yy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7866,54 +7859,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -56857,7 +56849,7 @@
     <col min="1" max="1" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="14.5">
       <c r="A1" s="22" t="s">
         <v>8</v>
       </c>
@@ -56871,7 +56863,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="14.5">
       <c r="A2" s="23" t="s">
         <v>85</v>
       </c>
@@ -56885,7 +56877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="14.5">
       <c r="A3" s="24" t="s">
         <v>272</v>
       </c>
@@ -56899,7 +56891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="14.5">
       <c r="A4" s="23" t="s">
         <v>487</v>
       </c>
@@ -56913,7 +56905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="14.5">
       <c r="A5" s="24" t="s">
         <v>12</v>
       </c>
@@ -56927,91 +56919,91 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="14.5">
       <c r="A6" s="23" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.5">
       <c r="A7" s="24" t="s">
         <v>951</v>
       </c>
       <c r="B7" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.5">
       <c r="A8" s="23" t="s">
         <v>1064</v>
       </c>
       <c r="B8" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="14.5">
       <c r="A9" s="24" t="s">
         <v>1270</v>
       </c>
       <c r="B9" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="14.5">
       <c r="A10" s="23" t="s">
         <v>1570</v>
       </c>
       <c r="B10" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="14.5">
       <c r="A11" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="14.5">
       <c r="A12" s="23" t="s">
         <v>715</v>
       </c>
@@ -57025,7 +57017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="14.5">
       <c r="A13" s="24" t="s">
         <v>771</v>
       </c>
@@ -57039,7 +57031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="14.5">
       <c r="A14" s="23" t="s">
         <v>2252</v>
       </c>
@@ -57054,7 +57046,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="23" t="s">
         <v>2548</v>
       </c>
       <c r="B16" s="14">
@@ -57083,7 +57075,7 @@
     <col min="1" max="1" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="14.5">
       <c r="A1" s="22" t="s">
         <v>9</v>
       </c>
@@ -57097,7 +57089,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" ht="14.5">
       <c r="A2" s="22" t="s">
         <v>86</v>
       </c>
@@ -57113,7 +57105,7 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="14.5">
       <c r="A3" s="22" t="s">
         <v>273</v>
       </c>
@@ -57128,7 +57120,7 @@
       </c>
       <c r="G3" s="26"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" ht="14.5">
       <c r="A4" s="22" t="s">
         <v>279</v>
       </c>
@@ -57143,22 +57135,22 @@
       </c>
       <c r="H4" s="26"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="14.5">
       <c r="A5" s="22" t="s">
         <v>451</v>
       </c>
       <c r="B5" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="14.5">
       <c r="A6" s="22" t="s">
         <v>870</v>
       </c>
@@ -57172,7 +57164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" ht="14.5">
       <c r="A7" s="22" t="s">
         <v>13</v>
       </c>
@@ -57187,7 +57179,7 @@
       </c>
       <c r="H7" s="27"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" ht="14.5">
       <c r="A8" s="22" t="s">
         <v>1271</v>
       </c>
@@ -57202,7 +57194,7 @@
       </c>
       <c r="H8" s="26"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="14.5">
       <c r="A9" s="22" t="s">
         <v>1337</v>
       </c>
@@ -57216,7 +57208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="14.5">
       <c r="A10" s="22" t="s">
         <v>716</v>
       </c>
@@ -57230,7 +57222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="14.5">
       <c r="A11" s="22" t="s">
         <v>925</v>
       </c>
@@ -57244,21 +57236,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="14.5">
       <c r="A12" s="22" t="s">
         <v>957</v>
       </c>
       <c r="B12" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.5">
       <c r="A13" s="22" t="s">
         <v>1074</v>
       </c>
@@ -57272,7 +57264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="14.5">
       <c r="A14" s="22" t="s">
         <v>27</v>
       </c>
@@ -57287,7 +57279,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="22" t="s">
         <v>2548</v>
       </c>
       <c r="B16" s="14">
